--- a/dados_extracao_msl.xlsx
+++ b/dados_extracao_msl.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6694a6633ef3c50c/01 - Documentos/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE1D48A-5883-2A4B-8E30-A3D0B7A7BF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{FEE1D48A-5883-2A4B-8E30-A3D0B7A7BF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBC8C157-5C24-9C4B-95E0-C98584BD568E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" xr2:uid="{C303722E-A4DB-9F4E-93FA-696E4C10ED42}"/>
+    <workbookView xWindow="52800" yWindow="-1980" windowWidth="19220" windowHeight="21000" xr2:uid="{C303722E-A4DB-9F4E-93FA-696E4C10ED42}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/dados_extracao_msl.xlsx
+++ b/dados_extracao_msl.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{FEE1D48A-5883-2A4B-8E30-A3D0B7A7BF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBC8C157-5C24-9C4B-95E0-C98584BD568E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ECC74C-95AC-204B-8618-10F0CDEB3D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52800" yWindow="-1980" windowWidth="19220" windowHeight="21000" xr2:uid="{C303722E-A4DB-9F4E-93FA-696E4C10ED42}"/>
+    <workbookView xWindow="52780" yWindow="-2200" windowWidth="19220" windowHeight="21000" xr2:uid="{C303722E-A4DB-9F4E-93FA-696E4C10ED42}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -324,9 +324,6 @@
     <t>Introduzir e avaliar o TutorCraftEase, que utiliza LLMs para auxiliar professores na criação de questões.</t>
   </si>
   <si>
-    <t>Ensino médio (física). 36 professores criando questões, 3 professores avaliando em teste cego.</t>
-  </si>
-  <si>
     <t>Assistente de Tarefas, Outro(s)</t>
   </si>
   <si>
@@ -827,21 +824,6 @@
   </si>
   <si>
     <r>
-      <t>6. Salminen et al. (2024)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF303030"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Communication Design for an Educational AI Chatbot: Analyzing Cipherbot’s Communication Style and Challenges</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>4. Pan et al. (2025)</t>
     </r>
     <r>
@@ -870,12 +852,29 @@
       <t xml:space="preserve"> Playing Dumb to Get Smart: Creating and Evaluating an LLM-based Teachable Agent within University Computer Science</t>
     </r>
   </si>
+  <si>
+    <t>Ensino fundamental e médio (física), K7-K12. 36 professores criando questões (17 do médio, 19 do fundamental)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. Salminen et al. (2024) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF303030"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Communication Design for an Educational AI Chatbot: Analyzing Cipherbot’s Communication Style and Challenges</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -908,6 +907,12 @@
       <color rgb="FF303030"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF303030"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1298,9 +1303,9 @@
     <col min="11" max="16384" width="55.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="34">
       <c r="A1" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
@@ -1396,7 +1401,7 @@
     </row>
     <row r="3" spans="1:26" ht="85">
       <c r="A3" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>20</v>
@@ -1492,7 +1497,7 @@
     </row>
     <row r="5" spans="1:26" ht="68">
       <c r="A5" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>39</v>
@@ -1588,7 +1593,7 @@
     </row>
     <row r="7" spans="1:26" ht="68">
       <c r="A7" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>57</v>
@@ -1636,7 +1641,7 @@
     </row>
     <row r="8" spans="1:26" ht="68">
       <c r="A8" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>66</v>
@@ -1684,7 +1689,7 @@
     </row>
     <row r="9" spans="1:26" ht="68">
       <c r="A9" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>74</v>
@@ -1732,34 +1737,34 @@
     </row>
     <row r="10" spans="1:26" ht="85">
       <c r="A10" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1780,34 +1785,34 @@
     </row>
     <row r="11" spans="1:26" ht="85">
       <c r="A11" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1828,34 +1833,34 @@
     </row>
     <row r="12" spans="1:26" ht="85">
       <c r="A12" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1876,34 +1881,34 @@
     </row>
     <row r="13" spans="1:26" ht="85">
       <c r="A13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1924,34 +1929,34 @@
     </row>
     <row r="14" spans="1:26" ht="74" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1972,34 +1977,34 @@
     </row>
     <row r="15" spans="1:26" ht="68">
       <c r="A15" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -2020,34 +2025,34 @@
     </row>
     <row r="16" spans="1:26" ht="68">
       <c r="A16" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -2068,34 +2073,34 @@
     </row>
     <row r="17" spans="1:26" ht="68">
       <c r="A17" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -2116,34 +2121,34 @@
     </row>
     <row r="18" spans="1:26" ht="68">
       <c r="A18" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -2164,34 +2169,34 @@
     </row>
     <row r="19" spans="1:26" ht="68">
       <c r="A19" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2212,34 +2217,34 @@
     </row>
     <row r="20" spans="1:26" ht="68">
       <c r="A20" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -2260,34 +2265,34 @@
     </row>
     <row r="21" spans="1:26" ht="68">
       <c r="A21" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
